--- a/idr_four_carrier_comparison.xlsx
+++ b/idr_four_carrier_comparison.xlsx
@@ -572,7 +572,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Average payor offer, % of QPA (5–95% trimmed)</a:t>
+              <a:t>Average payor offer, % of QPA (2–98% trimmed)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -777,7 +777,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Average prevailing offer (award), % of QPA (5–95% trimmed)</a:t>
+              <a:t>Average prevailing offer (award), % of QPA (2–98% trimmed)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1848,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1947,14 +1947,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Averages are 5-95% TRIMMED means: within each quarter x carrier, values outside</t>
+          <t xml:space="preserve">  Averages are 2-98% TRIMMED means: within each quarter x carrier, values outside</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the 5th-95th percentile are dropped before averaging. Untrimmed means are</t>
+          <t xml:space="preserve">         the 2nd-98th percentile are dropped before averaging. Untrimmed means are</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,106 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Medians (CMS's own convention) are included alongside for the robust read;</t>
+          <t xml:space="preserve">         Averages also EXCLUDE exact-zero offers/awards: a $0 offer is a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">         trimmed averages sit above medians because the distribution is right-skewed.</t>
+          <t xml:space="preserve">         no-offer-submitted record (default/non-engagement), not a real position</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         (5.8% of Aetna's and 5.7% of UnitedHealthcare's 2025 Q4 line items).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Scope notes</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Award (prevailing) averages additionally drop any award above 5,000% of</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BCBS (combined): every Blue-branded licensee (state BCBS plans, HCSC, Florida</t>
+          <t xml:space="preserve">         QPA before trimming - ratios that extreme reflect benchmark artifacts,</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Blue, Highmark, CareFirst, Horizon, Regence, ...) plus Anthem/Elevance.</t>
+          <t xml:space="preserve">         not payable amounts.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  UnitedHealthcare: the UHC brand only; UMR (UnitedHealth Group's TPA) is separate</t>
+          <t xml:space="preserve">         Medians (CMS's own convention) are included alongside, computed on the</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">         and not included.</t>
+          <t xml:space="preserve">         full unfiltered data for consistency with the dashboard;</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         trimmed averages sit above medians because the distribution is right-skewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Scope notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BCBS (combined): every Blue-branded licensee (state BCBS plans, HCSC, Florida</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Blue, Highmark, CareFirst, Horizon, Regence, ...) plus Anthem/Elevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  UnitedHealthcare: the UHC brand only; UMR (UnitedHealth Group's TPA) is separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         and not included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Source: CMS Federal IDR public use files, cleaned pipeline (this repo).</t>
         </is>
@@ -2124,10 +2173,10 @@
         <v>0.2642227705322524</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1</v>
+        <v>0.9996026860660325</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4.805306422335551</v>
+        <v>4.960712775851865</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1</v>
@@ -2157,10 +2206,10 @@
         <v>0.3267181500496139</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.094692411783075</v>
+        <v>1.088493822219999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2.332936109844455</v>
+        <v>2.426017818444498</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>1.05</v>
@@ -2190,10 +2239,10 @@
         <v>0.2348113530149322</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.045461445575298</v>
+        <v>1.04632367467896</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2.887848360655737</v>
+        <v>2.970394776799271</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>1</v>
@@ -2223,10 +2272,10 @@
         <v>0.3164197105444521</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.046174183514774</v>
+        <v>1.064494698117291</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3.076943888830403</v>
+        <v>3.152108546475359</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>1</v>
@@ -2256,10 +2305,10 @@
         <v>0.1461362816969114</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>0.9998571664011427</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.84590194629219</v>
+        <v>6.047691902756509</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>1</v>
@@ -2289,10 +2338,10 @@
         <v>0.2616475062667474</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.078078157553916</v>
+        <v>1.062267433895054</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.543790624384479</v>
+        <v>2.586289369620842</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1.05</v>
@@ -2322,10 +2371,10 @@
         <v>0.2949996306965064</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.092434907325684</v>
+        <v>1.113500873676637</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.05684388502724</v>
+        <v>3.133602274746757</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>1</v>
@@ -2355,10 +2404,10 @@
         <v>0.1911466026587888</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.202061049445005</v>
+        <v>1.221696520735928</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.675057982897973</v>
+        <v>2.815386596463115</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
@@ -2388,10 +2437,10 @@
         <v>0.1329124722743559</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.9998630136986303</v>
+        <v>0.9992271572627204</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.011282204119478</v>
+        <v>6.192156040268457</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>1</v>
@@ -2421,10 +2470,10 @@
         <v>0.2782831034916377</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.149268035190616</v>
+        <v>1.298659948780759</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.672756474603493</v>
+        <v>2.879809205819223</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>1</v>
@@ -2454,10 +2503,10 @@
         <v>0.2465844166597665</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.198682162277428</v>
+        <v>1.180175767030681</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.424596009482418</v>
+        <v>3.520561413508122</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>1.15</v>
@@ -2487,10 +2536,10 @@
         <v>0.1486336984179666</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.194492419478796</v>
+        <v>1.221259462718564</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.735014082703879</v>
+        <v>2.887962627335791</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>1.02</v>
@@ -2520,10 +2569,10 @@
         <v>0.08588328075709784</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.9998240416554449</v>
+        <v>0.9976040751800458</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5.324563740626379</v>
+        <v>5.552498693152117</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>1</v>
@@ -2553,10 +2602,10 @@
         <v>0.2084383930072281</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.442987757228445</v>
+        <v>1.428800103106071</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.69543199427046</v>
+        <v>4.609098484848484</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>1</v>
@@ -2586,10 +2635,10 @@
         <v>0.2400407424173834</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.469397702991453</v>
+        <v>1.501711133914828</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.08726309148265</v>
+        <v>4.246381082084932</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>1.25</v>
@@ -2619,10 +2668,10 @@
         <v>0.126438676911915</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.278770118552249</v>
+        <v>1.307960118056607</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.645952380952381</v>
+        <v>2.818165678333815</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>1.18</v>
@@ -2652,10 +2701,10 @@
         <v>0.1055792634740003</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.999318422148877</v>
+        <v>0.9966328728931695</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.607449407931834</v>
+        <v>5.869685010304839</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>1</v>
@@ -2685,10 +2734,10 @@
         <v>0.1266992930940729</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.194891298708037</v>
+        <v>1.426726030081819</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.295945890213222</v>
+        <v>5.282455215591235</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>1</v>
@@ -2718,10 +2767,10 @@
         <v>0.195741456995893</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.160276020379598</v>
+        <v>2.216741480996068</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.518416909471962</v>
+        <v>4.523271634615385</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>2</v>
@@ -2751,10 +2800,10 @@
         <v>0.1656088082901555</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.297593201754386</v>
+        <v>1.330670285081941</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.061975804388971</v>
+        <v>3.253694257941678</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>1.15</v>
@@ -2784,10 +2833,10 @@
         <v>0.08943222018716912</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9949623537391894</v>
+        <v>0.992953065539112</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.75654653727393</v>
+        <v>5.937929269695227</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>1</v>
@@ -2817,10 +2866,10 @@
         <v>0.215273596176822</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.209039924542306</v>
+        <v>1.406151682100574</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>7.013075350048844</v>
+        <v>6.184046459010914</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>1</v>
@@ -2850,10 +2899,10 @@
         <v>0.2475111507582516</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.832005648420279</v>
+        <v>2.993622093657897</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.562482056775576</v>
+        <v>4.616547071636012</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>2.59</v>
@@ -2883,10 +2932,10 @@
         <v>0.1957111246095106</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.365245679336922</v>
+        <v>1.413300160299225</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.804292478888801</v>
+        <v>3.984634038628895</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>1.13</v>
@@ -2916,10 +2965,10 @@
         <v>0.04754899634603527</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9977213685917505</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.822901194207803</v>
+        <v>5.800385963647505</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>1</v>
@@ -2949,10 +2998,10 @@
         <v>0.1981135511125678</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.169603725070763</v>
+        <v>1.38465031162421</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.180807980731454</v>
+        <v>6.415126356252184</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>1</v>
@@ -2982,10 +3031,10 @@
         <v>0.2180247517652716</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.721063868457064</v>
+        <v>2.850561548124539</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.308210764238095</v>
+        <v>4.373634398505433</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>2.54</v>
@@ -3015,10 +3064,10 @@
         <v>0.1757072273386555</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.450362876038818</v>
+        <v>1.501453605601789</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.355867920053471</v>
+        <v>4.434340204268468</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>1.18</v>
@@ -3051,7 +3100,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.579459799778085</v>
+        <v>5.548673243758861</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>1</v>
@@ -3081,10 +3130,10 @@
         <v>0.1452596848160783</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.140805616066136</v>
+        <v>1.335498804313495</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.55130434547441</v>
+        <v>7.416721737381413</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>1</v>
@@ -3114,10 +3163,10 @@
         <v>0.1646151404538962</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.034061123148215</v>
+        <v>3.292320739783395</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.546048258441904</v>
+        <v>4.61654587116367</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>2.63</v>
@@ -3147,10 +3196,10 @@
         <v>0.1766657761905431</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.411856213094854</v>
+        <v>1.457457432689294</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.531447872141603</v>
+        <v>4.597374568175674</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>1.15</v>
@@ -3183,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.879281048746008</v>
+        <v>4.881173394636015</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>1</v>
@@ -3213,10 +3262,10 @@
         <v>0.1396194510345061</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.182500703017738</v>
+        <v>1.335010454742177</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>9.480893293717841</v>
+        <v>7.823815289248093</v>
       </c>
       <c r="H35" s="4" t="n">
         <v>1</v>
@@ -3246,10 +3295,10 @@
         <v>0.1475372928377416</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3.033090436154737</v>
+        <v>3.304344636317305</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>4.671984453930322</v>
+        <v>4.77188179552004</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>2.31</v>
@@ -3279,10 +3328,10 @@
         <v>0.1345509659037212</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.227842252251009</v>
+        <v>1.274133473687967</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>4.282891695135839</v>
+        <v>4.437914852170553</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>1.04</v>
@@ -3312,10 +3361,10 @@
         <v>0.07112346150548365</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.9196255901230221</v>
+        <v>1.021038387703092</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>4.794016900868982</v>
+        <v>5.009452033522654</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>1</v>
@@ -3345,10 +3394,10 @@
         <v>0.1128370287949548</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1.177689238316324</v>
+        <v>1.331589166120888</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>9.616620419693946</v>
+        <v>7.827088080291405</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>1</v>
@@ -3378,10 +3427,10 @@
         <v>0.1807370158416758</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2.889901358050678</v>
+        <v>3.184677616168984</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>4.747726229645957</v>
+        <v>4.843295423989831</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>1.83</v>
@@ -3411,10 +3460,10 @@
         <v>0.1378038378946156</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1.136711737745955</v>
+        <v>1.263162776518111</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>4.715249329850849</v>
+        <v>4.862876489707475</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>1</v>
@@ -3444,10 +3493,10 @@
         <v>0.08634536827447847</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.9078993283348954</v>
+        <v>1.000238241476855</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>5.17062397760161</v>
+        <v>5.055003316592439</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>1</v>
@@ -3477,10 +3526,10 @@
         <v>0.1022767405175052</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1.322324068151238</v>
+        <v>1.46959929120979</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>8.157960217415525</v>
+        <v>7.449580509789852</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>1</v>
@@ -3510,10 +3559,10 @@
         <v>0.1923642462464532</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2.42934518322421</v>
+        <v>2.71300139730563</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>4.475084596520081</v>
+        <v>4.555180816904326</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>1.39</v>
@@ -3543,10 +3592,10 @@
         <v>0.1582175482247087</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1.112095318318002</v>
+        <v>1.241632969523469</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4.756970283118283</v>
+        <v>4.864557535318895</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>1</v>
@@ -3576,10 +3625,10 @@
         <v>0.09189746558367551</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.93379180085883</v>
+        <v>1.000408345774104</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>5.028550301521967</v>
+        <v>4.775439164022623</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>1</v>
@@ -3609,10 +3658,10 @@
         <v>0.1711682520155533</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.499880975022188</v>
+        <v>1.65658725440806</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>8.367486679613032</v>
+        <v>7.273255798086937</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>1</v>
@@ -3642,10 +3691,10 @@
         <v>0.2329928599761999</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1.977975293645118</v>
+        <v>2.148741367305847</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>4.569201464947749</v>
+        <v>4.543468588010615</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>1.25</v>
@@ -3675,10 +3724,10 @@
         <v>0.1836015967586142</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.13827546329427</v>
+        <v>1.280744178288247</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>5.121890475463112</v>
+        <v>4.977543845709715</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>1</v>
@@ -3758,10 +3807,10 @@
         <v>0.1923642462464532</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2.42934518322421</v>
+        <v>2.71300139730563</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4.475084596520081</v>
+        <v>4.555180816904326</v>
       </c>
     </row>
     <row r="4">
@@ -3777,10 +3826,10 @@
         <v>0.08634536827447847</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.9078993283348954</v>
+        <v>1.000238241476855</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.17062397760161</v>
+        <v>5.055003316592439</v>
       </c>
     </row>
     <row r="5">
@@ -3796,10 +3845,10 @@
         <v>0.1022767405175052</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.322324068151238</v>
+        <v>1.46959929120979</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>8.157960217415525</v>
+        <v>7.449580509789852</v>
       </c>
     </row>
     <row r="6">
@@ -3815,10 +3864,10 @@
         <v>0.1582175482247087</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.112095318318002</v>
+        <v>1.241632969523469</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.756970283118283</v>
+        <v>4.864557535318895</v>
       </c>
     </row>
     <row r="9">
@@ -3868,10 +3917,10 @@
         <v>0.2329928599761999</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.977975293645118</v>
+        <v>2.148741367305847</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.569201464947749</v>
+        <v>4.543468588010615</v>
       </c>
     </row>
     <row r="12">
@@ -3887,10 +3936,10 @@
         <v>0.09189746558367551</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.93379180085883</v>
+        <v>1.000408345774104</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.028550301521967</v>
+        <v>4.775439164022623</v>
       </c>
     </row>
     <row r="13">
@@ -3906,10 +3955,10 @@
         <v>0.1711682520155533</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.499880975022188</v>
+        <v>1.65658725440806</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.367486679613032</v>
+        <v>7.273255798086937</v>
       </c>
     </row>
     <row r="14">
@@ -3925,16 +3974,16 @@
         <v>0.1836015967586142</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.13827546329427</v>
+        <v>1.280744178288247</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.121890475463112</v>
+        <v>4.977543845709715</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Averages are 5-95% trimmed means; see README. Full history is in Data.</t>
+          <t>Averages are 2-98% trimmed means; see README. Full history is in Data.</t>
         </is>
       </c>
     </row>
@@ -4544,16 +4593,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1.045461445575298</v>
+        <v>1.04632367467896</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1</v>
+        <v>0.9996026860660325</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1.094692411783075</v>
+        <v>1.088493822219999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1.046174183514774</v>
+        <v>1.064494698117291</v>
       </c>
     </row>
     <row r="3">
@@ -4563,16 +4612,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1.092434907325684</v>
+        <v>1.113500873676637</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>0.9998571664011427</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1.078078157553916</v>
+        <v>1.062267433895054</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1.202061049445005</v>
+        <v>1.221696520735928</v>
       </c>
     </row>
     <row r="4">
@@ -4582,16 +4631,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1.198682162277428</v>
+        <v>1.180175767030681</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.9998630136986303</v>
+        <v>0.9992271572627204</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1.149268035190616</v>
+        <v>1.298659948780759</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.194492419478796</v>
+        <v>1.221259462718564</v>
       </c>
     </row>
     <row r="5">
@@ -4601,16 +4650,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1.469397702991453</v>
+        <v>1.501711133914828</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.9998240416554449</v>
+        <v>0.9976040751800458</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.442987757228445</v>
+        <v>1.428800103106071</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1.278770118552249</v>
+        <v>1.307960118056607</v>
       </c>
     </row>
     <row r="6">
@@ -4620,16 +4669,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2.160276020379598</v>
+        <v>2.216741480996068</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.999318422148877</v>
+        <v>0.9966328728931695</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.194891298708037</v>
+        <v>1.426726030081819</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.297593201754386</v>
+        <v>1.330670285081941</v>
       </c>
     </row>
     <row r="7">
@@ -4639,16 +4688,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2.832005648420279</v>
+        <v>2.993622093657897</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.9949623537391894</v>
+        <v>0.992953065539112</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.209039924542306</v>
+        <v>1.406151682100574</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.365245679336922</v>
+        <v>1.413300160299225</v>
       </c>
     </row>
     <row r="8">
@@ -4658,16 +4707,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2.721063868457064</v>
+        <v>2.850561548124539</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.9977213685917505</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.169603725070763</v>
+        <v>1.38465031162421</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.450362876038818</v>
+        <v>1.501453605601789</v>
       </c>
     </row>
     <row r="9">
@@ -4677,16 +4726,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3.034061123148215</v>
+        <v>3.292320739783395</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.140805616066136</v>
+        <v>1.335498804313495</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.411856213094854</v>
+        <v>1.457457432689294</v>
       </c>
     </row>
     <row r="10">
@@ -4696,16 +4745,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3.033090436154737</v>
+        <v>3.304344636317305</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.182500703017738</v>
+        <v>1.335010454742177</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.227842252251009</v>
+        <v>1.274133473687967</v>
       </c>
     </row>
     <row r="11">
@@ -4715,16 +4764,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2.889901358050678</v>
+        <v>3.184677616168984</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9196255901230221</v>
+        <v>1.021038387703092</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.177689238316324</v>
+        <v>1.331589166120888</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.136711737745955</v>
+        <v>1.263162776518111</v>
       </c>
     </row>
     <row r="12">
@@ -4734,16 +4783,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2.42934518322421</v>
+        <v>2.71300139730563</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.9078993283348954</v>
+        <v>1.000238241476855</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.322324068151238</v>
+        <v>1.46959929120979</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.112095318318002</v>
+        <v>1.241632969523469</v>
       </c>
     </row>
     <row r="13">
@@ -4753,16 +4802,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1.977975293645118</v>
+        <v>2.148741367305847</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.93379180085883</v>
+        <v>1.000408345774104</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.499880975022188</v>
+        <v>1.65658725440806</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.13827546329427</v>
+        <v>1.280744178288247</v>
       </c>
     </row>
   </sheetData>
@@ -4820,16 +4869,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2.887848360655737</v>
+        <v>2.970394776799271</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4.805306422335551</v>
+        <v>4.960712775851865</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>2.332936109844455</v>
+        <v>2.426017818444498</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3.076943888830403</v>
+        <v>3.152108546475359</v>
       </c>
     </row>
     <row r="3">
@@ -4839,16 +4888,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3.05684388502724</v>
+        <v>3.133602274746757</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>5.84590194629219</v>
+        <v>6.047691902756509</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2.543790624384479</v>
+        <v>2.586289369620842</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.675057982897973</v>
+        <v>2.815386596463115</v>
       </c>
     </row>
     <row r="4">
@@ -4858,16 +4907,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3.424596009482418</v>
+        <v>3.520561413508122</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.011282204119478</v>
+        <v>6.192156040268457</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.672756474603493</v>
+        <v>2.879809205819223</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.735014082703879</v>
+        <v>2.887962627335791</v>
       </c>
     </row>
     <row r="5">
@@ -4877,16 +4926,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4.08726309148265</v>
+        <v>4.246381082084932</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5.324563740626379</v>
+        <v>5.552498693152117</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.69543199427046</v>
+        <v>4.609098484848484</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.645952380952381</v>
+        <v>2.818165678333815</v>
       </c>
     </row>
     <row r="6">
@@ -4896,16 +4945,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4.518416909471962</v>
+        <v>4.523271634615385</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.607449407931834</v>
+        <v>5.869685010304839</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.295945890213222</v>
+        <v>5.282455215591235</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.061975804388971</v>
+        <v>3.253694257941678</v>
       </c>
     </row>
     <row r="7">
@@ -4915,16 +4964,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4.562482056775576</v>
+        <v>4.616547071636012</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.75654653727393</v>
+        <v>5.937929269695227</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.013075350048844</v>
+        <v>6.184046459010914</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.804292478888801</v>
+        <v>3.984634038628895</v>
       </c>
     </row>
     <row r="8">
@@ -4934,16 +4983,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>4.308210764238095</v>
+        <v>4.373634398505433</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.822901194207803</v>
+        <v>5.800385963647505</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.180807980731454</v>
+        <v>6.415126356252184</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.355867920053471</v>
+        <v>4.434340204268468</v>
       </c>
     </row>
     <row r="9">
@@ -4953,16 +5002,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4.546048258441904</v>
+        <v>4.61654587116367</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.579459799778085</v>
+        <v>5.548673243758861</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.55130434547441</v>
+        <v>7.416721737381413</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.531447872141603</v>
+        <v>4.597374568175674</v>
       </c>
     </row>
     <row r="10">
@@ -4972,16 +5021,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4.671984453930322</v>
+        <v>4.77188179552004</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.879281048746008</v>
+        <v>4.881173394636015</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.480893293717841</v>
+        <v>7.823815289248093</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.282891695135839</v>
+        <v>4.437914852170553</v>
       </c>
     </row>
     <row r="11">
@@ -4991,16 +5040,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4.747726229645957</v>
+        <v>4.843295423989831</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.794016900868982</v>
+        <v>5.009452033522654</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9.616620419693946</v>
+        <v>7.827088080291405</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.715249329850849</v>
+        <v>4.862876489707475</v>
       </c>
     </row>
     <row r="12">
@@ -5010,16 +5059,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>4.475084596520081</v>
+        <v>4.555180816904326</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.17062397760161</v>
+        <v>5.055003316592439</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.157960217415525</v>
+        <v>7.449580509789852</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.756970283118283</v>
+        <v>4.864557535318895</v>
       </c>
     </row>
     <row r="13">
@@ -5029,16 +5078,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4.569201464947749</v>
+        <v>4.543468588010615</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.028550301521967</v>
+        <v>4.775439164022623</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8.367486679613032</v>
+        <v>7.273255798086937</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.121890475463112</v>
+        <v>4.977543845709715</v>
       </c>
     </row>
   </sheetData>
